--- a/Portas lógicas.xlsx
+++ b/Portas lógicas.xlsx
@@ -8,12 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\visualg\2026a\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E2C6355C-D1F5-4579-A777-1199E921BF98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FDA759A-7552-42E6-8E48-0EEF07A9DCB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{67F9F3DC-136D-446C-BAEC-7175026F27B4}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="15600" windowHeight="11040" activeTab="1" xr2:uid="{67F9F3DC-136D-446C-BAEC-7175026F27B4}"/>
   </bookViews>
   <sheets>
-    <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
+    <sheet name="AND" sheetId="2" r:id="rId1"/>
+    <sheet name="Exemplo tabela verdade 21" sheetId="9" r:id="rId2"/>
+    <sheet name="NOT" sheetId="5" r:id="rId3"/>
+    <sheet name="NOR" sheetId="7" r:id="rId4"/>
+    <sheet name="XNOR" sheetId="8" r:id="rId5"/>
+    <sheet name="OR" sheetId="3" r:id="rId6"/>
+    <sheet name="XOR" sheetId="4" r:id="rId7"/>
+    <sheet name="NAND" sheetId="6" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,6 +40,38 @@
     </ext>
   </extLst>
 </workbook>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="9">
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>F</t>
+  </si>
+  <si>
+    <t>Resultado</t>
+  </si>
+  <si>
+    <t>V</t>
+  </si>
+  <si>
+    <t>Reuultado</t>
+  </si>
+  <si>
+    <t>A*B</t>
+  </si>
+  <si>
+    <t>X</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -83,6 +122,219 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>33973</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>321339</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>137327</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Imagem 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{59ABD7E8-E024-6C31-DB8E-FEEC9B9AAF65}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="1858377" y="0"/>
+          <a:ext cx="4544308" cy="2232827"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>600075</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>180975</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>104961</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>47713</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Imagem 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{44210673-C303-D3D7-D876-179F3B21182B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3038475" y="752475"/>
+          <a:ext cx="1333686" cy="628738"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>371475</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>85725</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>228750</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>133436</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Imagem 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1D023CCF-E974-912B-3D50-70B95D6207C4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2200275" y="276225"/>
+          <a:ext cx="1076475" cy="619211"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>276225</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>457481</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>133471</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Imagem 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FE301567-061F-46C4-9060-28F3B50166A4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2105025" y="790575"/>
+          <a:ext cx="2010056" cy="866896"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -401,10 +653,595 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4BAC221-6F78-4036-A4B8-B3EB01BFCC4B}">
-  <dimension ref="A1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EDEF1472-5ABF-42F5-A031-70BC6F6AB540}">
+  <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{827C9255-EF2C-4E78-B35D-26E66C9F013B}">
+  <dimension ref="A1:E9"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C6" t="s">
+        <v>3</v>
+      </c>
+      <c r="D6" t="s">
+        <v>3</v>
+      </c>
+      <c r="E6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" t="s">
+        <v>3</v>
+      </c>
+      <c r="C7" t="s">
+        <v>5</v>
+      </c>
+      <c r="D7" t="s">
+        <v>3</v>
+      </c>
+      <c r="E7" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>5</v>
+      </c>
+      <c r="B8" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8" t="s">
+        <v>3</v>
+      </c>
+      <c r="D8" t="s">
+        <v>5</v>
+      </c>
+      <c r="E8" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>5</v>
+      </c>
+      <c r="B9" t="s">
+        <v>5</v>
+      </c>
+      <c r="C9" t="s">
+        <v>5</v>
+      </c>
+      <c r="D9" t="s">
+        <v>5</v>
+      </c>
+      <c r="E9" t="s">
+        <v>5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6C7162D-0C4A-48F5-BA88-8E5C63C5B9E6}">
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D2E269B-E4E8-4181-9786-B82648A0FAED}">
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="3" width="11.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" t="s">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A76FEF5-45CC-4C38-808C-B572F05EB6F0}">
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B045C786-44BC-401F-AEB0-342559DFCC92}">
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D1CAA8FA-D194-4127-ABBC-15D4758B6A95}">
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" t="s">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4DFC9ACC-AF91-4D15-B7A7-6399F47F873D}">
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" t="s">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>